--- a/x_Trade Ideas/260316_Meat Producers.xlsx
+++ b/x_Trade Ideas/260316_Meat Producers.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Documents\models\x_Trade Ideas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8CDBA0-BB74-412D-A5E1-9E86FFDEAE6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218D57C5-E0CF-413C-9CBE-DF5AD929AEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="98">
   <si>
     <t>Company Name</t>
   </si>
@@ -216,6 +217,120 @@
   </si>
   <si>
     <t>47.65</t>
+  </si>
+  <si>
+    <t>Poultry Market Early-Warning Dashboard</t>
+  </si>
+  <si>
+    <t>Indicator</t>
+  </si>
+  <si>
+    <t>Why it matters</t>
+  </si>
+  <si>
+    <t>Bullish signal for poultry stocks</t>
+  </si>
+  <si>
+    <t>Bearish signal</t>
+  </si>
+  <si>
+    <t>1. Corn futures</t>
+  </si>
+  <si>
+    <t>Largest feed input (~50–60% of feed)</t>
+  </si>
+  <si>
+    <t>Falling corn prices</t>
+  </si>
+  <si>
+    <t>Rising corn prices</t>
+  </si>
+  <si>
+    <t>2. Soybean meal futures</t>
+  </si>
+  <si>
+    <t>Key protein feed component</t>
+  </si>
+  <si>
+    <t>Declining soybean meal</t>
+  </si>
+  <si>
+    <t>Rapid spike in soybean meal</t>
+  </si>
+  <si>
+    <t>3. Chicken breast prices (boneless/skinless)</t>
+  </si>
+  <si>
+    <t>Benchmark wholesale chicken price</t>
+  </si>
+  <si>
+    <t>Rising breast prices</t>
+  </si>
+  <si>
+    <t>Falling breast prices</t>
+  </si>
+  <si>
+    <t>4. Wing prices</t>
+  </si>
+  <si>
+    <t>Important for restaurant demand</t>
+  </si>
+  <si>
+    <t>Strong wing demand</t>
+  </si>
+  <si>
+    <t>Weak wing demand</t>
+  </si>
+  <si>
+    <t>5. USDA broiler chick placements</t>
+  </si>
+  <si>
+    <t>Predicts supply 6–8 weeks ahead</t>
+  </si>
+  <si>
+    <t>Falling placements</t>
+  </si>
+  <si>
+    <t>Rising placements</t>
+  </si>
+  <si>
+    <t>6. Cold storage chicken inventories</t>
+  </si>
+  <si>
+    <t>Indicates oversupply</t>
+  </si>
+  <si>
+    <t>Declining inventories</t>
+  </si>
+  <si>
+    <t>Rising inventories</t>
+  </si>
+  <si>
+    <t>7. Restaurant traffic / foodservice demand</t>
+  </si>
+  <si>
+    <t>Chicken consumption indicator</t>
+  </si>
+  <si>
+    <t>Strong restaurant demand</t>
+  </si>
+  <si>
+    <t>Weak traffic</t>
+  </si>
+  <si>
+    <t>8. Export demand (Mexico / China)</t>
+  </si>
+  <si>
+    <t>Global price support</t>
+  </si>
+  <si>
+    <t>Strong exports</t>
+  </si>
+  <si>
+    <t>Export restrictions</t>
+  </si>
+  <si>
+    <t>https://www.nass.usda.gov/Surveys/Guide_to_NASS_Surveys/Broiler_Hatchery/index.php</t>
   </si>
 </sst>
 </file>
@@ -223,10 +338,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,8 +356,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -252,6 +383,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -265,11 +402,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -278,10 +416,13 @@
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -1169,4 +1310,160 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D7FA135-ED6B-4366-A894-2AA85EFFB9BC}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E8" r:id="rId1" xr:uid="{CED34B58-B76C-411D-9527-FF4E3E8FA251}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>